--- a/Output/cleaned_data.xlsx
+++ b/Output/cleaned_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3287,6 +3287,7666 @@
         <v>905.76</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648720664067/MR RAJU /YESB/q
+ 996801404/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>40</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>865.76</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648720705266/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>10</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>855.76</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648728361796/GOURAV K/YESB/q
+ 363440705/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>24</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>831.76</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648731161612/SURESH  /YESB/q
+ 710870349/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>50</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>781.76</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648731258057/GOPAL  D/YESB/q
+ 481719172/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>80</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>701.76</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/612199688245/supermoney/YESB
+ /supermoney/Su   0097736162097 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="E149" t="n">
+        <v>732.49</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648731307739/GOURAV K/YESB/q
+ 131273556/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>14</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>718.49</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648732606665/TOSH  KU/SBIN/t
+ oshkumar2/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>500</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>218.49</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/953257458146/SHWETA  /SBIN/7
+ 225820307/Paym   0097736162097 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>300</v>
+      </c>
+      <c r="E152" t="n">
+        <v>518.49</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648732624506/TOSH  KU/SBIN/t
+ oshkumar2/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>500</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/612124480424/DHANENDR/HDFC/
+ dhanendra7/UPI   0097736162097 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1018.49</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648732859665/PRAGATI /HDFC/8
+ 819888563/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>300</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>718.49</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648835847723/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>30</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>688.49</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/612222742189/TOSH  KU/SBIN/
+ toshkumar2/UPI   0097737162096 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1688.49</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648841892987/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>30</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1658.49</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648845601459/SURESH  /YESB/q
+ 473035596/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>50</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1608.49</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612274930087/Amazon P/RATN/a
+ mazonpayl/Requ   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>5</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1603.49</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648845844302/GOURAV K/YESB/q
+ 131273556/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>30</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1573.49</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648950145385/AJAY MEHAR/YESB
+ /q365807494/Pa   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>40</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1533.49</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648950201538/PREMPAL /YESB/q
+ 122324793/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>70</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1463.49</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648957083002/GOURAV K/YESB/q
+ 131273556/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>35</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1428.49</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/648960137693/DEO KUMA/YESB/p
+ aytmqr6re/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>76</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1352.49</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649064440792/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>30</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1322.49</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649070610920/ABHISEK /YESB/q
+ 510548773/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>30</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1292.49</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649070779650/M/S.TRIB/ICIC/e
+ azypay.58/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>60</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1232.49</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649071047451/GOURAV K/YESB/q
+ 363440705/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>24</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1208.49</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649073972564/Mrs LAKS/FDRL/
+ bharatpe.9/Pay   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>50</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1158.49</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649074280831/KEVAL YA/SBIN/8
+ 236031938/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>55</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1103.49</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649074376507/GOURAV K/YESB/q
+ 131273556/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>25</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1078.49</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649176445563/Indian O/YESB/q
+ 345798136/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>130</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>948.49</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649185456551/GOURAV K/YESB/q
+ 131273556/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>24</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>924.49</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/801089475090/CHOWA RA/SBIN/9
+ 165697262/Paym   0097733162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E175" t="n">
+        <v>7924.49</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/825744301256/SOURABH /ICIC/
+ srbverma10/UPI   0097733162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E176" t="n">
+        <v>8924.49</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649189787218/ZOMATO/HDFC/pay
+ zomato@/Paid v   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>8799.790000000001</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/103242753914/ZOMATO/HDFC/pa
+ yzomato@/Order   0097733162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="E178" t="n">
+        <v>8924.49</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649291215913/SAHUL HA/YESB/q
+ 979548969/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>30</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>8894.49</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649291253331/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>10</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>8884.49</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649292782480/AJAY MEHAR/YESB
+ /q332659512/Pa   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>40</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>8844.49</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649292864463/MD GULAM/CNRB/7
+ 257924113/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>10</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>8834.49</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649292930297/PREMPAL /YESB/q
+ 152264044/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>105</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>8729.49</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649298399656/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>30</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>8699.49</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/302067296820/DURGA SH/SBIN/d
+ urgaschou/Rent   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>5699.49</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649299232460/M/S.TRIB/ICIC/e
+ azypay.58/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>130</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>5569.49</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612602997809/MR PRASH/YESB/q
+ 871589976/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>60</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>5509.49</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612707752085/ZOMATO/HDFC/pay
+ zomato@/Paid v   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>5418.41</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612713302741/ABHISEK /YESB/q
+ 650730337/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>30</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>5388.41</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612713896347/GOURAV K/YESB/q
+ 667324871/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>40</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>5348.41</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612714644108/TAPENDRA/YESB/q
+ 655939557/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>50</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>5298.41</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612717895435/GOURAV K/YESB/q
+ 667324871/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>20</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>5278.41</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612823554419/ZOMATO LTD/HDFC
+ /zomatoltd3/Pa   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>5171.88</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612823907166/NIRMAL K/PUNB/7
+ 999257520/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>20</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>5151.88</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612828794280/GOURAV K/YESB/q
+ 667324871/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>39</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>5112.88</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612831465418/MRS KHUS/YESB/q
+ 607072220/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>50</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>5062.88</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612831701816/SURESH  /YESB/q
+ 739462265/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>60</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>5002.88</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612936747550/AJAY MEHAR/YESB
+ /q332659512/Pa   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>40</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>4962.88</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612936814033/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>10</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>4952.88</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/205743129976/Jio/YESB/paybi
+ l3066/Sent usi   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>19</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>4933.88</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612943136329/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>40</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>4893.88</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612946501798/ZOMATO L/YESB/z
+ omato-ord/Zoma   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>4833.61</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/612946513901/Swiggy Ltd/UTIB
+ /swiggyupi@/Pa   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>82</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>4751.61</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613052097386/ZOMATO/HDFC/pay
+ zomato@/Paid v   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>4660.53</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613058086585/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>30</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>4630.53</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613058434359/GOURAV K/YESB/q
+ 667324871/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>24</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>4606.53</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613062047708/SURESH  /YESB/q
+ 739462265/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>50</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>4556.53</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613062082517/M/S.TRIB/ICIC/e
+ azypay.58/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>130</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>4426.53</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613062125384/Mr Vinod/YESB/q
+ 165479108/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>70</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>4356.53</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613166635027/AJAY MEHAR/YESB
+ /q332659512/Pa   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>40</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>4316.53</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613168682523/JIOMART/HDFC/ji
+ omartb2b/Payme   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4251.03</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613173478566/GOURAV K/YESB/q
+ 667324871/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>24</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>4227.03</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613176323159/DEO KUMA/YESB/p
+ aytmqr6re/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>70</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>4157.03</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613176521153/GOURAV K/YESB/q
+ 667324871/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>50</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>4107.03</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613282833353/SWIGGY/ICIC/upi
+ swiggy@/Paid v   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>89</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>4018.03</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613288058486/GOURAV K/YESB/q
+ 363440705/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>54</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>3964.03</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613290776350/SURESH  /YESB/q
+ 115699830/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>50</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>3914.03</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613250885381/upi juspay/YESB
+ /paytm-7620/Tr   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>3751.78</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/649801521591/upi juspay/YESB
+ /paytm-7620/ex   0097733162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="E219" t="n">
+        <v>3914.03</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613393781569/Indian R/YESB/p
+ aytm-6467/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>100</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>3814.03</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613393785000/BABA KHA/YESB/q
+ 115995800/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>20</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>3794.03</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613351919770/Indian R/SBIN/b
+ dpg2.ir@s/Sent   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>3706.78</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613396383873/BUDHSAN /SBIN/9
+ 907262053/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>20</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>3686.78</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613396434484/SANTOSH /YESB/q
+ 536258373/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>40</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>3646.78</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649900951390/M/S.DAWAT/ICIC/
+ eazypay.ic/Pai   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>230</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>3416.78</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649902824899/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>40</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>3376.78</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/649905843015/MA DANTE/AIRP/3
+ 420401395/Paym   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>30</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>3346.78</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/604505845101/Swiggy Ltd/UTIB
+ /swiggyupi@/Pa   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>118</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>3228.78</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650009935022/SONU HAI/YESB/q
+ 552685402/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>50</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>3178.78</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650009941926/AKASHRAJ/BARB/7
+ 389026077/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>30</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>3148.78</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650010366662/RUPA BAI/YESB/p
+ aytm.s1sd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>15</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>3133.78</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650011739019/MUNNALAL/YESB/q
+ 366467937/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>20</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>3113.78</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650012433542/ROPPEN T/AIRP/r
+ oppentran/Paym   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>19</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>3094.78</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650012577481/Swiggy Ltd/UTIB
+ /swiggyupi@/Pa   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>104</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>2990.78</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650017652669/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>40</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>2950.78</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650021777622/ROMA DEV/YESB/p
+ aytm.s22e/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>40</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>2910.78</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650126255303/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>10</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>2900.78</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613534843954/JIO/KKBK/rel
+ iancere/Pay   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>19</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>2881.78</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650127197603/PRATAP N/BARB/6
+ 263563155/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>95</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>2786.78</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613566829746/CHAYA PA/YESB/p
+ aytm.s25j/Sent   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>40</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>2746.78</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650132148482/SUMIT KU/YESB/q
+ 251802691/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>40</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2706.78</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650132324048/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>20</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>2686.78</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650136692593/ROMA DEV/YESB/p
+ aytm.s22e/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>25</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>2661.78</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650246823589/CHAYA PA/YESB/p
+ aytm.s25j/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>40</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>2621.78</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650247120942/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>20</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>2601.78</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650251827067/ROMA DEV/YESB/p
+ aytm.s22e/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>25</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>2576.78</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650361057496/Dhamtari/YESB/p
+ aytmqr6vq/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>90</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>2486.78</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650361443643/MR RAMRA/YESB/q
+ 503463984/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>40</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>2446.78</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650366924659/ROMA DEV/YESB/p
+ aytm.s22e/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>25</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>2421.78</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650475767182/Shri Bik/YESB/p
+ aytmqr6pc/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>30</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>2391.78</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650475896754/MR DEEPA/YESB/q
+ 099668507/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>80</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>2311.78</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650476040560/MR RAMRA/YESB/q
+ 503463984/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>40</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>2271.78</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650481720832/New Bika/YESB/p
+ aytmqr6kc/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>20</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>2251.78</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650481787770/ROMA DEV/YESB/p
+ aytm.s22e/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>37</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>2214.78</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613987631446/IRCTCTOU/HDFC/i
+ rctctouri/Tran   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2052.53</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650590704807/Rapido/YESB/pay
+ tm-7688/Paid v   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>63</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1989.53</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/206503201677/Airtel/YESB/pay
+ air7673/Sent u   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>33</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1956.53</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/613989851442/JIO/KKBK/rel
+ iancere/Pay   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>19</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1937.53</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650591301026/PAPPU KH/YESB/p
+ aytmqr5jo/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>50</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1887.53</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650591475753/MR LAKHA/YESB/q
+ 086384197/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>35</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1852.53</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/650595253478/DIPENDRA/FDRL/
+ bharatpe.9/Pay   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>40</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1812.53</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614006528965/SURESH K/YESB/q
+ 413663851/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>55</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1757.53</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614115936007/ZOMATO L/HDFC/z
+ omatofd.p/UPII   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>105.58</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1651.95</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614122139209/GOURAV K/YESB/q
+ 152428676/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>10</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1641.95</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/100551281005/MRS SUSH/YESB/
+ Q070924923/Pay   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>20</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1621.95</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>WDL TFR   IMPS/614120643295/HDFC-xx151-PRAG
+ ATI /Transfer   0098292162098 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>100</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1521.95</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/100551388192/RAHUL PR/YESB/
+ paytmqr281/Pay   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>10</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1511.95</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614125794586/Swiggy Ltd/UTIB
+ /swiggyupi@/Pa   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>90</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1421.95</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614228769969/AJAY MEHAR/YESB
+ /q365807494/Pa   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>40</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1381.95</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614228841143/MR SHARM/YESB/q
+ 533230479/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>30</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1351.95</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614235828133/GOURAV K/YESB/q
+ 037514874/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>90</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1261.95</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614237507779/SURESH  /YESB/q
+ 115699830/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>50</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1211.95</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614343966492/ZOMATO LTD/HDFC
+ /zomatoltd3/Pa   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1120.87</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614350863394/GOURAV K/YESB/q
+ 152428676/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>25</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1095.87</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614351089367/M/S.TRIB/ICIC/e
+ azypay.58/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>110</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>985.87</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614353025384/SHRILAL /YESB/p
+ aytmqr736/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>80</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>905.87</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614353506759/DEO KUMA/YESB/p
+ aytmqr6re/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>60</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>845.87</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614460486174/SWIGGY/ICIC/upi
+ swiggy@/Paid v   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>82</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>763.87</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/987030561446/Google P/utib/p
+ laystore1/Mand   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>89</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>674.87</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/725092183888/CHOWA RA/SBIN/9
+ 165697262/Paym   0097738162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E280" t="n">
+        <v>2674.87</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614465812219/FRIENDS /HDFC/v
+ yapar.175/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>140</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>2534.87</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614572560678/ZOMATO L/INDB/z
+ omato2.pa/UPII   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>121.53</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>2413.34</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/614586487957/supermoney/YESB
+ /supermoney/Su   0097732162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>0</v>
+      </c>
+      <c r="D283" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="E283" t="n">
+        <v>2468.82</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614578720563/Mrs Shil/YESB/p
+ aytmqr72g/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>40</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>2428.82</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614579049694/GOURAV K/YESB/q
+ 152428676/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>50</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>2378.82</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/206947610029/upi juspay/YESB
+ /paytm-7620/Tr   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>2216.57</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614685413294/Ankit Si/AIRP/b
+ hadoriyaa/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>10</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>2206.57</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614687505993/JUHI  DEEP/SBIN
+ /7898389718/Pa   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>89</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>2117.57</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/606838280376/IRCTCTOU/HDFC/i
+ rctctouri/Tran   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1955.32</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614691666431/FAGURAM /ICIC/8
+ 085108531/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>43</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1912.32</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614691683115/SANTOSH /YESB/q
+ 536258373/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>20</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1892.32</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614691714571/POHE WALA/YESB/
+ paytm.s224/Pai   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>45</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1847.32</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614691946962/SHUBHAM /YESB/p
+ aytmqr5cv/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>20</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1827.32</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614627934847/IRCTC Ra/YESB/i
+ rctcpgonl/Paym   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>147.25</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1680.07</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/978850925364/DURGA SH/SBIN/9
+ 303343052/Paym   0097733162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>1956</v>
+      </c>
+      <c r="E295" t="n">
+        <v>3636.07</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651311745896/Shyam au/YESB/q
+ 490675301/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>610</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>3026.07</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651413678206/VIKASH P/YESB/q
+ 719736162/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>27</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>2999.07</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651414160418/SHIV ANA/CBIN/2
+ 025071900/9377   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>50</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>2949.07</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651415041612/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>35</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>2914.07</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/614944204602/Blinkit/HDFC/bl
+ inkit.pa/UPIIn   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>160</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>2754.07</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651640665772/ZOMATO L/HDFC/z
+ omatofd.p/UPII   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>2685.04</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651645158835/Swiggy Ltd/UTIB
+ /swiggyupi@/Pa   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>133</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>2552.04</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651653329794/Mrs ASHA/YESB/p
+ aytmqr6zc/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>15</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>2537.04</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651768121092/RAJENDRA/YESB/q
+ 584024109/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>20</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>2517.04</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651768129112/RAJENDRA/YESB/q
+ 584024109/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>4</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>2513.04</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651768852271/RAHUL PA/YESB/q
+ 031464366/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>180</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>2333.04</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651769399005/GANESH S/YESB/p
+ aytmqr6ub/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>33</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>2300.04</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615226885974/Amazon Pay/UTIB
+ /amazonpayl/Re   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>1335.71</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>964.33</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651882018815/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>10</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>954.33</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651882119644/Mrs ASHA/YESB/p
+ aytmqr6zc/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>70</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>884.33</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651996819720/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>20</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>864.33</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651998196829/AKASH BH/YESB/q
+ 399186146/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>50</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>814.33</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651998394394/SNEHA KU/BARB/8
+ 251092239/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>10</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>804.33</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/651999433462/Shubham /YESB/p
+ aytm.d860/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>352</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>452.33</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/615419300844/DHANENDR/HDFC/
+ dhanendra7/UPI   0097734162099 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>0</v>
+      </c>
+      <c r="D315" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E315" t="n">
+        <v>2952.33</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/615448752719/SHUSHANT/SBIN/
+ namankmrya/UPI   0097734162099 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>0</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E316" t="n">
+        <v>3952.33</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615412572431/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>20</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>3932.33</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615414637502/RUPESH K/YESB/q
+ 893528103/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>77</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>3855.33</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615414821386/Rahul so/YESB/p
+ aytmqr6oo/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>100</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>3755.33</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615414847301/KULESHWA/YESB/q
+ 460935448/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>20</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>3735.33</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615522081378/Swiggy Ltd/UTIB
+ /swiggyupi@/Pa   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>100</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>3635.33</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615525148495/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>10</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>3625.33</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615525223089/GOPAL DE/PSIB/6
+ 263473611/Merc   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>20</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>3605.33</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615525264709/JITENDRA/YESB/q
+ 990421268/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>20</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>3585.33</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615529838214/SHUBHAM /YESB/p
+ aytm.d904/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>186</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>3399.33</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615530002131/Mr LAXMA/YESB/p
+ aytm.s225/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>150</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>3249.33</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615530246422/Krishna /YESB/q
+ 651612561/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>110</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>3139.33</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615642238218/ADITYA F/ICIC/a
+ dityafrui/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>110</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>3029.33</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615642627968/GOPAL DE/PSIB/6
+ 263473611/Merc   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>30</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>2999.33</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/615750046993/PRAGATI /HDFC/8
+ 819888563/Paid   0097737162096 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E330" t="n">
+        <v>6999.33</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/607473815094/Sushil B/YESB/p
+ aytmqr6rt/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>30</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>6969.33</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/307504376374/GURMEET /UCBA/8
+ 966869797/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>2469.33</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/307505204687/MRS KASH/YESB/q
+ 011472423/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>50</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>2419.33</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/607479758965/Mrs ASHA/YESB/p
+ aytmqr6zc/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>90</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>2329.33</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/138096381576/SOURABH /ICIC/
+ srbverma10/UPI   0097737162096 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E335" t="n">
+        <v>4829.33</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/307526877641/Miss Pra/FINO/8
+ 819888563/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" t="n">
+        <v>4828.33</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/307527078325/PRAGATI /HDFC/b
+ hardwajpr/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>1</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>4827.33</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/307527539810/Pusti Am/YESB/p
+ aytmqr6vd/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>10</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>4817.33</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/307538608814/Blinkit/HDFC/bl
+ inkit.pa/UPIIn   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>172</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>4645.33</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/307542700722/VIKAS   /YESB/q
+ 642875058/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>35</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>4610.33</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615864475753/DAKSHIN /YESB/p
+ aytmqr6qc/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>40</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>4570.33</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615869309001/PRAGATI /HDFC/b
+ hardwajpr/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>2570.33</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615873961899/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>10</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>2560.33</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/607592274500/RAJ KISH/YESB/p
+ aytmqr5yc/Sent   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>50</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>2510.33</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615981031877/KANHEIYA/YESB/q
+ 963398064/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>40</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>2470.33</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615988594362/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>25</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>2445.33</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615988857240/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>10</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>2435.33</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615992226587/SANDIP K/YESB/p
+ aytmqr6sf/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>90</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>2345.33</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/615992841003/Ekta jui/YESB/p
+ aytm.s24o/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>180</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>2165.33</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652604263878/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>20</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>2145.33</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652608892498/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>10</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>2135.33</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652713936795/Shree Ra/YESB/p
+ aytmqr6np/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>110</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>2025.33</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652714749406/RAKHEE D/YESB/q
+ 080592617/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>50</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1975.33</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652714917231/RAKHEE D/YESB/q
+ 080592617/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>50</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1925.33</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652715874881/Ekta jui/YESB/p
+ aytm.s24o/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>60</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1865.33</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652720332218/CHAYA PA/YESB/p
+ aytm.s25j/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>20</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1845.33</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652720344198/SUMIT KU/YESB/q
+ 251802691/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>20</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1825.33</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652720888676/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>10</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" t="n">
+        <v>1815.33</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652723320277/SHUBHAM /YESB/p
+ aytm.d904/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>361.23</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1454.1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652723362218/MR RAMRA/YESB/q
+ 503463984/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>40</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1414.1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652723591607/MR RAMRA/YESB/q
+ 503463984/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>20</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1394.1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652831539619/Super Mo/ICIC/e
+ urosuper@/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>39</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1355.1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652832872949/ZOMATO LTD/HDFC
+ /zomatoltd3/Pa   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>106.73</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1248.37</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652835664439/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>25</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0</v>
+      </c>
+      <c r="E364" t="n">
+        <v>1223.37</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652840697951/Pusti Am/YESB/p
+ aytmqr71i/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>35</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>1188.37</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652944502711/DAKSHIN /YESB/p
+ aytmqr6qc/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>90</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>1098.37</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652944599302/JITENDRA/YESB/q
+ 990421268/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>10</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1088.37</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652945898624/Pusti Am/YESB/p
+ aytmqr71i/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>10</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" t="n">
+        <v>1078.37</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652946277615/Karo kan/YESB/q
+ 960417216/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>250</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" t="n">
+        <v>828.37</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/652947664700/RAMRATAN/YESB/p
+ aytm.s1nx/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>20</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0</v>
+      </c>
+      <c r="E370" t="n">
+        <v>808.37</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653068302216/Ravi Kum/AIRP/9
+ 174378757/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>20</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0</v>
+      </c>
+      <c r="E371" t="n">
+        <v>788.37</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/607927375933/Vinayak /YESB/q
+ 212381534/Sent   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>110</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="n">
+        <v>678.37</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653181740198/Super Mo/ICIC/e
+ urosuper@/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>39</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" t="n">
+        <v>639.37</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653181884146/JIO/KKBK/rel
+ iancere/Pay   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>39</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0</v>
+      </c>
+      <c r="E374" t="n">
+        <v>600.37</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616706011990/Ashish K/YESB/p
+ aytm.s250/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>15</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0</v>
+      </c>
+      <c r="E375" t="n">
+        <v>585.37</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616831550137/CHAYA PA/YESB/p
+ aytm.s25j/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>20</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>565.37</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616831804229/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>10</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0</v>
+      </c>
+      <c r="E377" t="n">
+        <v>555.37</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616831901883/VIKAS   /YESB/q
+ 642875058/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>30</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0</v>
+      </c>
+      <c r="E378" t="n">
+        <v>525.37</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616937415385/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>20</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>505.37</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616944839708/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>40</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="n">
+        <v>465.37</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616946382334/SUNIL KU/YESB/q
+ 782123523/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>20</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" t="n">
+        <v>445.37</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616946412348/SUNIL KU/YESB/q
+ 782123523/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>3</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0</v>
+      </c>
+      <c r="E382" t="n">
+        <v>442.37</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616946522092/Suraj Le/YESB/p
+ aytmqr65y/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>140</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" t="n">
+        <v>302.37</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/296555692383/CHOWA RA/SBIN/9
+ 165697262/Paym   0097735162098 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>0</v>
+      </c>
+      <c r="D384" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E384" t="n">
+        <v>5302.37</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/616950479689/SANDEEP /YESB/q
+ 018565048/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>35</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0</v>
+      </c>
+      <c r="E385" t="n">
+        <v>5267.37</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617053775264/DAKSHIN /YESB/p
+ aytmqr6qc/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>100</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" t="n">
+        <v>5167.37</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617059701431/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>20</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="n">
+        <v>5147.37</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617059721934/VIKAS   /YESB/q
+ 642875058/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>30</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" t="n">
+        <v>5117.37</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617064466627/Amazon P/RATN/
+ amazonpayl/You   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>752.16</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="n">
+        <v>4365.21</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617064517185/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>10</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" t="n">
+        <v>4355.21</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/617085259801/supermoney/YESB
+ /supermoney/Su   0097736162097 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>0</v>
+      </c>
+      <c r="D391" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="E391" t="n">
+        <v>4395.88</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/617064705700/PRAGATI /HDFC/8
+ 819888563/Paid   0097736162097 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>0</v>
+      </c>
+      <c r="D392" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E392" t="n">
+        <v>9895.879999999999</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617166886704/KOHINOOR/KKBK/7
+ 724948382/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>70</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" t="n">
+        <v>9825.879999999999</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/608875071210/RASHMI  /SBIN/9
+ 039578559/Sent   0097737162096 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>0</v>
+      </c>
+      <c r="D394" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E394" t="n">
+        <v>24825.88</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/308876135422/RASHMI S/BARB/9
+ 039578559/Sent   0097737162096 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>0</v>
+      </c>
+      <c r="D395" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E395" t="n">
+        <v>29825.88</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617168770931/upi juspay/YESB
+ /paytm-7620/Tr   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>4404.95</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0</v>
+      </c>
+      <c r="E396" t="n">
+        <v>25420.93</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617168946645/SANAT KU/YESB/p
+ aytm.s1q9/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>10</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="n">
+        <v>25410.93</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617177151722/SANAT KU/YESB/q
+ 279065006/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>10</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0</v>
+      </c>
+      <c r="E398" t="n">
+        <v>25400.93</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/208929972589/upi juspay/YESB
+ /paytm-7620/Tr   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>2003.6</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0</v>
+      </c>
+      <c r="E399" t="n">
+        <v>23397.33</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/208930407770/upi juspay/YESB
+ /paytm-7620/Tr   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>1263.6</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0</v>
+      </c>
+      <c r="E400" t="n">
+        <v>22133.73</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617180048843/SUNIL KU/YESB/q
+ 782123523/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>23</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" t="n">
+        <v>22110.73</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617180790801/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>35</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0</v>
+      </c>
+      <c r="E402" t="n">
+        <v>22075.73</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/208939406515/upi juspay/YESB
+ /paytm-7620/Tr   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>2323.6</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" t="n">
+        <v>19752.13</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617181168709/PRAGATI /HDFC/b
+ hardwajpr/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>30</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>19722.13</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617182189909/ROMA DEV/YESB/p
+ aytm.s22e/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>25</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0</v>
+      </c>
+      <c r="E405" t="n">
+        <v>19697.13</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/617203932613/upi juspay/YESB
+ /paytm-7620/ex   0097738162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>0</v>
+      </c>
+      <c r="D406" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E406" t="n">
+        <v>21547.13</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/617204196182/upi juspay/YESB
+ /paytm-7620/ex   0097738162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D407" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E407" t="n">
+        <v>22657.13</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/308980059057/Yateesh/BARB/6
+ 267222698/Gas   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>350</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>22307.13</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/617298107178/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>35</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="n">
+        <v>22272.13</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653900297993/DAKSHIN /YESB/p
+ aytmqr6qc/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>160</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="n">
+        <v>22112.13</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653900411704/JITENDRA/YESB/q
+ 457724520/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>5</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="n">
+        <v>22107.13</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653910115093/Super Mo/ICIC/e
+ urosuper@/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>39</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" t="n">
+        <v>22068.13</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653911611094/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>35</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>22033.13</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653911801852/TOSH  KU/SBIN/t
+ oshkumar2/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>20033.13</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/653911807971/TOSH  KU/SBIN/t
+ oshkumar2/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0</v>
+      </c>
+      <c r="E415" t="n">
+        <v>17033.13</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654025970603/CHAYA PA/YESB/p
+ aytm.s25j/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>40</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>16993.13</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654026417334/SANAT KU/YESB/q
+ 473617082/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>45</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>16948.13</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654026475667/SHARAD K/YESB/q
+ 146433807/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>30</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>16918.13</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654132052887/DAKSHIN /YESB/p
+ aytmqr6qc/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>80</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>16838.13</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654132268049/MAHAVIR /YESB/q
+ 400511367/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>550</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0</v>
+      </c>
+      <c r="E420" t="n">
+        <v>16288.13</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654132366712/JITENDRA/YESB/q
+ 457724520/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>10</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>16278.13</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/167907451756/Google P/utib/p
+ laystore1/Mand   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>89</v>
+      </c>
+      <c r="D422" t="n">
+        <v>0</v>
+      </c>
+      <c r="E422" t="n">
+        <v>16189.13</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654138397884/BHUNESHW/YESB/q
+ 597624451/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>50</v>
+      </c>
+      <c r="D423" t="n">
+        <v>0</v>
+      </c>
+      <c r="E423" t="n">
+        <v>16139.13</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654140055201/CITYKART/YESB/p
+ aytm.d929/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>3569</v>
+      </c>
+      <c r="D424" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" t="n">
+        <v>12570.13</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654140407921/MANISH S/YESB/p
+ aytm.s23d/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>20</v>
+      </c>
+      <c r="D425" t="n">
+        <v>0</v>
+      </c>
+      <c r="E425" t="n">
+        <v>12550.13</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654143232291/Maa gana/YESB/p
+ aytmqr64c/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>35</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>12515.13</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654246706530/DAKSHIN /YESB/p
+ aytmqr6qc/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>100</v>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="n">
+        <v>12415.13</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654246855301/UMESH NA/SBIN/i
+ ndianmo19/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>20</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="n">
+        <v>12395.13</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/609177592448/Mr MOHAM/YESB/q
+ 740851257/Sent   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>15</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="n">
+        <v>12380.13</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654247650962/RITESH A/YESB/p
+ aytmqr6a1/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>20</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="n">
+        <v>12360.13</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654361178180/Gourthy /AIRP/
+ bharatpe.9/Pay   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>289</v>
+      </c>
+      <c r="D431" t="n">
+        <v>0</v>
+      </c>
+      <c r="E431" t="n">
+        <v>12095.13</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654367652405/MR SARVE/YESB/q
+ 818331575/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>15</v>
+      </c>
+      <c r="D432" t="n">
+        <v>0</v>
+      </c>
+      <c r="E432" t="n">
+        <v>12080.13</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654367691408/MR SARVE/YESB/q
+ 818331575/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>10</v>
+      </c>
+      <c r="D433" t="n">
+        <v>0</v>
+      </c>
+      <c r="E433" t="n">
+        <v>12070.13</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654368525380/SURAPANG/SBIN/9
+ 618628385/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>50</v>
+      </c>
+      <c r="D434" t="n">
+        <v>0</v>
+      </c>
+      <c r="E434" t="n">
+        <v>12020.13</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/209379894382/Yadagiri/YESB/p
+ aytm-8386/Sent   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>60</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="n">
+        <v>11960.13</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654369216592/P RAMAKR/YESB/p
+ aytmqr665/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>60</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0</v>
+      </c>
+      <c r="E436" t="n">
+        <v>11900.13</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654369450486/P RAMAKR/YESB/p
+ aytmqr665/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>25</v>
+      </c>
+      <c r="D437" t="n">
+        <v>0</v>
+      </c>
+      <c r="E437" t="n">
+        <v>11875.13</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654371209053/M S SRIV/ICIC/i
+ bkpos.ep0/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>25</v>
+      </c>
+      <c r="D438" t="n">
+        <v>0</v>
+      </c>
+      <c r="E438" t="n">
+        <v>11850.13</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654372668729/Maram Bh/YESB/p
+ aytmqr6x5/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>150</v>
+      </c>
+      <c r="D439" t="n">
+        <v>0</v>
+      </c>
+      <c r="E439" t="n">
+        <v>11700.13</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654477659022/THE REGA/YESB/y
+ espay.mab/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>10</v>
+      </c>
+      <c r="D440" t="n">
+        <v>0</v>
+      </c>
+      <c r="E440" t="n">
+        <v>11690.13</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/654594519753/APOLLO P/YESB/a
+ pollophar/Paym   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D441" t="n">
+        <v>0</v>
+      </c>
+      <c r="E441" t="n">
+        <v>11647.93</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/209568426786/Zepto/YESB/zept
+ oonlin/Sent us   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>99</v>
+      </c>
+      <c r="D442" t="n">
+        <v>0</v>
+      </c>
+      <c r="E442" t="n">
+        <v>11548.93</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618010658887/ZOMATO L/YESB/z
+ omato-ord/Zoma   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>920.8</v>
+      </c>
+      <c r="D443" t="n">
+        <v>0</v>
+      </c>
+      <c r="E443" t="n">
+        <v>10628.13</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618016870485/APOLLO P/YESB/a
+ pollophar/Paym   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>148.59</v>
+      </c>
+      <c r="D444" t="n">
+        <v>0</v>
+      </c>
+      <c r="E444" t="n">
+        <v>10479.54</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/618108215764/upi juspay/YESB
+ /paytm-7620/ex   0097733162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>0</v>
+      </c>
+      <c r="D445" t="n">
+        <v>2170</v>
+      </c>
+      <c r="E445" t="n">
+        <v>12649.54</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/209648798490/Zepto/YESB/zept
+ oonlin/Sent us   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>54</v>
+      </c>
+      <c r="D446" t="n">
+        <v>0</v>
+      </c>
+      <c r="E446" t="n">
+        <v>12595.54</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/309504202915/ZEPTO MA/INDB/z
+ eptomarke/Sent   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>63</v>
+      </c>
+      <c r="D447" t="n">
+        <v>0</v>
+      </c>
+      <c r="E447" t="n">
+        <v>12532.54</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618241251883/CHETLAPA/SBIN/c
+ hatlapall/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>210</v>
+      </c>
+      <c r="D448" t="n">
+        <v>0</v>
+      </c>
+      <c r="E448" t="n">
+        <v>12322.54</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618241362719/HARIYANA/INDB/b
+ ajajpay.6/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>60</v>
+      </c>
+      <c r="D449" t="n">
+        <v>0</v>
+      </c>
+      <c r="E449" t="n">
+        <v>12262.54</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618241421386/PRABIN S/YESB/p
+ aytmqr6yd/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>10</v>
+      </c>
+      <c r="D450" t="n">
+        <v>0</v>
+      </c>
+      <c r="E450" t="n">
+        <v>12252.54</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/309564528654/Moin Syed/YESB/
+ paytmqr6q4/Sen   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>20</v>
+      </c>
+      <c r="D451" t="n">
+        <v>0</v>
+      </c>
+      <c r="E451" t="n">
+        <v>12232.54</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618245728613/KAILASH /YESB/q
+ 139398978/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>15</v>
+      </c>
+      <c r="D452" t="n">
+        <v>0</v>
+      </c>
+      <c r="E452" t="n">
+        <v>12217.54</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618349235149/MOHAMMAD/UBIN/9
+ 669354072/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>32</v>
+      </c>
+      <c r="D453" t="n">
+        <v>0</v>
+      </c>
+      <c r="E453" t="n">
+        <v>12185.54</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618358617045/ZOMATO LTD/HDFC
+ /zomatoltd3/Pa   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>153.03</v>
+      </c>
+      <c r="D454" t="n">
+        <v>0</v>
+      </c>
+      <c r="E454" t="n">
+        <v>12032.51</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618358634058/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>45</v>
+      </c>
+      <c r="D455" t="n">
+        <v>0</v>
+      </c>
+      <c r="E455" t="n">
+        <v>11987.51</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618361966985/MANISH S/YESB/p
+ aytm.s23d/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>10</v>
+      </c>
+      <c r="D456" t="n">
+        <v>0</v>
+      </c>
+      <c r="E456" t="n">
+        <v>11977.51</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618362175545/RMR FUELS/YESB/
+ q240315426/Pai   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>210</v>
+      </c>
+      <c r="D457" t="n">
+        <v>0</v>
+      </c>
+      <c r="E457" t="n">
+        <v>11767.51</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618363063078/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>20</v>
+      </c>
+      <c r="D458" t="n">
+        <v>0</v>
+      </c>
+      <c r="E458" t="n">
+        <v>11747.51</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618363170699/SIDDHART/UTIB/p
+ inelabs.1/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>180</v>
+      </c>
+      <c r="D459" t="n">
+        <v>0</v>
+      </c>
+      <c r="E459" t="n">
+        <v>11567.51</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618363333009/DRON KUM/SBIN/9
+ 098034812/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>154</v>
+      </c>
+      <c r="D460" t="n">
+        <v>0</v>
+      </c>
+      <c r="E460" t="n">
+        <v>11413.51</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618467119576/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>10</v>
+      </c>
+      <c r="D461" t="n">
+        <v>0</v>
+      </c>
+      <c r="E461" t="n">
+        <v>11403.51</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618467177949/JITENDRA/YESB/q
+ 457724520/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>41</v>
+      </c>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>11362.51</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618467738949/SONU HAI/YESB/q
+ 552685402/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>50</v>
+      </c>
+      <c r="D463" t="n">
+        <v>0</v>
+      </c>
+      <c r="E463" t="n">
+        <v>11312.51</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618472283019/RAKHEE D/YESB/q
+ 080592617/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>50</v>
+      </c>
+      <c r="D464" t="n">
+        <v>0</v>
+      </c>
+      <c r="E464" t="n">
+        <v>11262.51</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618473871977/Mr NAND /CBIN/9
+ 893162506/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>15</v>
+      </c>
+      <c r="D465" t="n">
+        <v>0</v>
+      </c>
+      <c r="E465" t="n">
+        <v>11247.51</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618474017806/SHUJAT  /YESB/q
+ 774241680/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>15</v>
+      </c>
+      <c r="D466" t="n">
+        <v>0</v>
+      </c>
+      <c r="E466" t="n">
+        <v>11232.51</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618478660359/SANAT KU/YESB/q
+ 279065006/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>35</v>
+      </c>
+      <c r="D467" t="n">
+        <v>0</v>
+      </c>
+      <c r="E467" t="n">
+        <v>11197.51</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618478662317/SANAT KU/YESB/q
+ 279065006/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>5</v>
+      </c>
+      <c r="D468" t="n">
+        <v>0</v>
+      </c>
+      <c r="E468" t="n">
+        <v>11192.51</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618478729411/SIDDHI V/YESB/p
+ aytmqr6cl/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>90</v>
+      </c>
+      <c r="D469" t="n">
+        <v>0</v>
+      </c>
+      <c r="E469" t="n">
+        <v>11102.51</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618588716976/Euronet /UTIB/e
+ urosuperr/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>39</v>
+      </c>
+      <c r="D470" t="n">
+        <v>0</v>
+      </c>
+      <c r="E470" t="n">
+        <v>11063.51</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618591361135/MOHD KHA/YESB/p
+ aytmqr6wp/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>30</v>
+      </c>
+      <c r="D471" t="n">
+        <v>0</v>
+      </c>
+      <c r="E471" t="n">
+        <v>11033.51</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618592360625/SATYAVEE/YESB/q
+ 109016713/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>60</v>
+      </c>
+      <c r="D472" t="n">
+        <v>0</v>
+      </c>
+      <c r="E472" t="n">
+        <v>10973.51</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618592517254/DURGESHW/YESB/q
+ 543669656/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>30</v>
+      </c>
+      <c r="D473" t="n">
+        <v>0</v>
+      </c>
+      <c r="E473" t="n">
+        <v>10943.51</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618592774798/Mohammad/YESB/p
+ aytm.s276/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>20</v>
+      </c>
+      <c r="D474" t="n">
+        <v>0</v>
+      </c>
+      <c r="E474" t="n">
+        <v>10923.51</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618593406983/DHIRAJ T/YESB/p
+ aytmqr63k/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>60</v>
+      </c>
+      <c r="D475" t="n">
+        <v>0</v>
+      </c>
+      <c r="E475" t="n">
+        <v>10863.51</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618594056855/BROWN LA/HDFC/v
+ yapar.175/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>139</v>
+      </c>
+      <c r="D476" t="n">
+        <v>0</v>
+      </c>
+      <c r="E476" t="n">
+        <v>10724.51</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618595075839/VIKAS   /YESB/q
+ 642875058/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>65</v>
+      </c>
+      <c r="D477" t="n">
+        <v>0</v>
+      </c>
+      <c r="E477" t="n">
+        <v>10659.51</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/618697380106/ANNAPURN/YESB/q
+ 709831612/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>80</v>
+      </c>
+      <c r="D478" t="n">
+        <v>0</v>
+      </c>
+      <c r="E478" t="n">
+        <v>10579.51</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655203979254/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>80</v>
+      </c>
+      <c r="D479" t="n">
+        <v>0</v>
+      </c>
+      <c r="E479" t="n">
+        <v>10499.51</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655204631920/Shree Ra/YESB/p
+ aytmqr6se/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>150</v>
+      </c>
+      <c r="D480" t="n">
+        <v>0</v>
+      </c>
+      <c r="E480" t="n">
+        <v>10349.51</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655206516795/Aman Kes/YESB/p
+ aytm.s1t3/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>90</v>
+      </c>
+      <c r="D481" t="n">
+        <v>0</v>
+      </c>
+      <c r="E481" t="n">
+        <v>10259.51</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655207225735/SIHOGYA /YESB/q
+ 012185868/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>26</v>
+      </c>
+      <c r="D482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E482" t="n">
+        <v>10233.51</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655207312195/ROMA DEV/YESB/p
+ aytm.s22e/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>60</v>
+      </c>
+      <c r="D483" t="n">
+        <v>0</v>
+      </c>
+      <c r="E483" t="n">
+        <v>10173.51</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655210193100/Dominos /YESB/p
+ aytm-5195/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>414.75</v>
+      </c>
+      <c r="D484" t="n">
+        <v>0</v>
+      </c>
+      <c r="E484" t="n">
+        <v>9758.76</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/618741567243/DHANENDR/HDFC/
+ dhanendra7/UPI   0097732162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>0</v>
+      </c>
+      <c r="D485" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E485" t="n">
+        <v>10758.76</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655315794651/SANAT KU/YESB/q
+ 279065006/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>25</v>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="n">
+        <v>10733.76</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655315908562/PREM SIN/YESB/p
+ aytm.s225/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>40</v>
+      </c>
+      <c r="D487" t="n">
+        <v>0</v>
+      </c>
+      <c r="E487" t="n">
+        <v>10693.76</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655319803308/RAJU SAHU/YESB/
+ paytm.s20l/Pai   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>30</v>
+      </c>
+      <c r="D488" t="n">
+        <v>0</v>
+      </c>
+      <c r="E488" t="n">
+        <v>10663.76</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655320489768/Pramod S/AIRP/9
+ 005122265/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>70</v>
+      </c>
+      <c r="D489" t="n">
+        <v>0</v>
+      </c>
+      <c r="E489" t="n">
+        <v>10593.76</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655320871078/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>45</v>
+      </c>
+      <c r="D490" t="n">
+        <v>0</v>
+      </c>
+      <c r="E490" t="n">
+        <v>10548.76</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655325517262/ROMA DEV/YESB/p
+ aytm.s22e/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>40</v>
+      </c>
+      <c r="D491" t="n">
+        <v>0</v>
+      </c>
+      <c r="E491" t="n">
+        <v>10508.76</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655426977089/ZOMATO L/HDFC/z
+ omatofd.p/UPII   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>141.48</v>
+      </c>
+      <c r="D492" t="n">
+        <v>0</v>
+      </c>
+      <c r="E492" t="n">
+        <v>10367.28</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655436078914/RAJENDRA/YESB/q
+ 342101643/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>39</v>
+      </c>
+      <c r="D493" t="n">
+        <v>0</v>
+      </c>
+      <c r="E493" t="n">
+        <v>10328.28</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655436287558/Lokesh K/AIRP/8
+ 827722769/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>50</v>
+      </c>
+      <c r="D494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E494" t="n">
+        <v>10278.28</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655441813574/DEVI LAL/YESB/p
+ aytmqr700/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>50</v>
+      </c>
+      <c r="D495" t="n">
+        <v>0</v>
+      </c>
+      <c r="E495" t="n">
+        <v>10228.28</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655442108701/RAKHEE D/YESB/q
+ 080592617/Paid   0097691162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>100</v>
+      </c>
+      <c r="D496" t="n">
+        <v>0</v>
+      </c>
+      <c r="E496" t="n">
+        <v>10128.28</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/618858301696/supermoney/YESB
+ /supermoney/Su   0097733162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>0</v>
+      </c>
+      <c r="D497" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E497" t="n">
+        <v>10177.98</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655546091467/DAKSHIN /YESB/p
+ aytmqr6qc/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>80</v>
+      </c>
+      <c r="D498" t="n">
+        <v>0</v>
+      </c>
+      <c r="E498" t="n">
+        <v>10097.98</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655549493543/SHARAD K/YESB/q
+ 146433807/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>93</v>
+      </c>
+      <c r="D499" t="n">
+        <v>0</v>
+      </c>
+      <c r="E499" t="n">
+        <v>10004.98</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655552720100/RAMESH S/YESB/p
+ aytm.s1o3/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>30</v>
+      </c>
+      <c r="D500" t="n">
+        <v>0</v>
+      </c>
+      <c r="E500" t="n">
+        <v>9974.98</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655552892014/SANAT KU/YESB/q
+ 279065006/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>10</v>
+      </c>
+      <c r="D501" t="n">
+        <v>0</v>
+      </c>
+      <c r="E501" t="n">
+        <v>9964.98</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655553080907/M S ANAN/ICIC/i
+ bkpos.ep2/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>265</v>
+      </c>
+      <c r="D502" t="n">
+        <v>0</v>
+      </c>
+      <c r="E502" t="n">
+        <v>9699.98</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655556876556/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>35</v>
+      </c>
+      <c r="D503" t="n">
+        <v>0</v>
+      </c>
+      <c r="E503" t="n">
+        <v>9664.98</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/110179995481/LinkedIn/ICIC/l
+ inkedin.b/Mand   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>2</v>
+      </c>
+      <c r="D504" t="n">
+        <v>0</v>
+      </c>
+      <c r="E504" t="n">
+        <v>9662.98</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/210322710677/Airtel/YESB/air
+ tel-pre/Sent u   0097692162094 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>39</v>
+      </c>
+      <c r="D505" t="n">
+        <v>0</v>
+      </c>
+      <c r="E505" t="n">
+        <v>9623.98</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655668987307/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>25</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+      <c r="E506" t="n">
+        <v>9598.98</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>DEP TFR   UPI/CR/258715193463/C R DEV /HDFC/c
+ rdev@axl/retur   0097735162098 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>0</v>
+      </c>
+      <c r="D507" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E507" t="n">
+        <v>12598.98</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655672179512/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097693162093 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>26</v>
+      </c>
+      <c r="D508" t="n">
+        <v>0</v>
+      </c>
+      <c r="E508" t="n">
+        <v>12572.98</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655785444051/Shri Bik/YESB/p
+ aytmqr6pc/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>50</v>
+      </c>
+      <c r="D509" t="n">
+        <v>0</v>
+      </c>
+      <c r="E509" t="n">
+        <v>12524.98</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655785773317/SANAT KU/UBIN/
+ bharatpe.9/Pay   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>26</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0</v>
+      </c>
+      <c r="E510" t="n">
+        <v>12498.98</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655787641520/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>25</v>
+      </c>
+      <c r="D511" t="n">
+        <v>0</v>
+      </c>
+      <c r="E511" t="n">
+        <v>12473.98</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655789434425/YASHWANT/SBIN/8
+ 889505210/Paid   0097694162092 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>125</v>
+      </c>
+      <c r="D512" t="n">
+        <v>0</v>
+      </c>
+      <c r="E512" t="n">
+        <v>12348.98</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619225341015/Airtel/YESB/pay
+ air7673/Sent u   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>39</v>
+      </c>
+      <c r="D513" t="n">
+        <v>0</v>
+      </c>
+      <c r="E513" t="n">
+        <v>12309.98</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655897847998/MADHAV FFC/HDFC
+ /vyapar.173/Pa   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>170</v>
+      </c>
+      <c r="D514" t="n">
+        <v>0</v>
+      </c>
+      <c r="E514" t="n">
+        <v>12139.98</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/655898109744/Navin Ku/YESB/p
+ aytm.s1ta/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>40</v>
+      </c>
+      <c r="D515" t="n">
+        <v>0</v>
+      </c>
+      <c r="E515" t="n">
+        <v>12099.98</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619201375455/MOHIT KU/YESB/p
+ aytm.s2fp/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>50</v>
+      </c>
+      <c r="D516" t="n">
+        <v>0</v>
+      </c>
+      <c r="E516" t="n">
+        <v>12049.98</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619201402033/Gupta ja/YESB/q
+ 098215716/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>20</v>
+      </c>
+      <c r="D517" t="n">
+        <v>0</v>
+      </c>
+      <c r="E517" t="n">
+        <v>12029.98</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619206224859/AMRIKA S/YESB/q
+ 524478397/Paid   0097695162091 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>80</v>
+      </c>
+      <c r="D518" t="n">
+        <v>0</v>
+      </c>
+      <c r="E518" t="n">
+        <v>11949.98</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619306939102/JYOTSNA /YESB/q
+ 168825793/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>20</v>
+      </c>
+      <c r="D519" t="n">
+        <v>0</v>
+      </c>
+      <c r="E519" t="n">
+        <v>11929.98</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619307028541/Monika S/YESB/p
+ aytm.s1w3/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>35</v>
+      </c>
+      <c r="D520" t="n">
+        <v>0</v>
+      </c>
+      <c r="E520" t="n">
+        <v>11894.98</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619316311926/Shri Bik/YESB/p
+ aytmqr6pc/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>30</v>
+      </c>
+      <c r="D521" t="n">
+        <v>0</v>
+      </c>
+      <c r="E521" t="n">
+        <v>11864.98</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619316584156/SANAT KU/YESB/q
+ 279065006/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>25</v>
+      </c>
+      <c r="D522" t="n">
+        <v>0</v>
+      </c>
+      <c r="E522" t="n">
+        <v>11839.98</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619319784241/Pusti Am/YESB/p
+ aytmqr6vd/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>45</v>
+      </c>
+      <c r="D523" t="n">
+        <v>0</v>
+      </c>
+      <c r="E523" t="n">
+        <v>11794.98</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619320771639/Ajay Kum/KKBK/8
+ 966992699/Paid   0097696162090 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>462</v>
+      </c>
+      <c r="D524" t="n">
+        <v>0</v>
+      </c>
+      <c r="E524" t="n">
+        <v>11332.98</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>WDL TFR   UPI/DR/619422729223/VIKAS   /YESB/q
+ 642875058/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>27</v>
+      </c>
+      <c r="D525" t="n">
+        <v>0</v>
+      </c>
+      <c r="E525" t="n">
+        <v>11305.98</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>WDL TFR    UPI/DR/619422740299/VIKAS   /YESB/
+ q642875058/Paid   0097690162095 AT 18092 GURUR</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>10</v>
+      </c>
+      <c r="D526" t="n">
+        <v>0</v>
+      </c>
+      <c r="E526" t="n">
+        <v>11295.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
